--- a/courses/BUS-314-International-Corporate-Finance/accounting-ratios/_scenarios/BUS314_MSFT_Scenario.xlsx
+++ b/courses/BUS-314-International-Corporate-Finance/accounting-ratios/_scenarios/BUS314_MSFT_Scenario.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\shidler\BUS-314-International-Corporate-Finance\accounting-ratios\_scenarios\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\shidler\courses\BUS-314-International-Corporate-Finance\accounting-ratios\_scenarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB0E56F1-95CD-4560-B2D2-0C42D0CA70F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA0DE6B4-613C-4F2D-AFB5-C5FAF242E7E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1580,10 +1580,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1775,7 +1771,9 @@
   <we:alternateReferences>
     <we:reference id="wa200009404" version="1.0.0.8" store="" storeType="OMEX"/>
   </we:alternateReferences>
-  <we:properties/>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;d70527c2-fb52-4b26-b1ad-7c5d964b7a48&quot;"/>
+  </we:properties>
   <we:bindings/>
   <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </we:webextension>
@@ -2290,7 +2288,8 @@
         <v>17645</v>
       </c>
       <c r="D7" s="25">
-        <v>7.1984562789141698E-2</v>
+        <f>IF(C$4=0,0,C7/C$4)</f>
+        <v>7.198456278914174E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
@@ -2338,7 +2337,8 @@
         <v>2935</v>
       </c>
       <c r="D11" s="25">
-        <v>1.19736294579842E-2</v>
+        <f>IF(C$4=0,0,C11/C$4)</f>
+        <v>1.1973629457984188E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
@@ -2373,7 +2373,8 @@
         <v>21631</v>
       </c>
       <c r="D14" s="25">
-        <v>6.9149239970300494E-2</v>
+        <f>IF(C$4=0,0,C14/C$4)</f>
+        <v>8.8245853085402365E-2</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
@@ -3043,8 +3044,8 @@
         <v>116</v>
       </c>
       <c r="C19" s="34">
-        <f>'Income Statement'!C8*(1-C8)</f>
-        <v>87867.818998423929</v>
+        <f>'Income Statement'!C15+(1-C8)*'Income Statement'!C11</f>
+        <v>90492.620477921417</v>
       </c>
       <c r="D19" s="31" t="s">
         <v>117</v>
